--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1220,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1244,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1513,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1735,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2309,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2357,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2376,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2401,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2412,1022 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1330,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1621,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1696,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1740,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1870,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1918,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1957,7 +1981,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1996,32 +2020,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2029,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,33 +2081,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2290,7 +2322,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2362,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2527,7 +2559,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2620,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2731,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2753,7 +2785,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3068,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3151,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3205,7 +3237,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3213,22 +3245,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3261,12 +3293,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3324,7 +3356,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3334,7 +3366,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3372,12 +3404,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3391,7 +3423,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3426,6 +3458,799 @@
       </c>
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2139,32 +2139,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2172,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,17 +2200,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2216,13 +2220,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2472,32 +2480,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2505,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2529,17 +2541,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2549,17 +2561,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2659,7 +2671,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2731,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2858,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2897,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2957,7 +2969,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3195,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3249,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3532,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3574,7 +3586,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3647,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,7 +3762,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3804,7 +3816,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3877,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +3988,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4030,7 +4042,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4103,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4202,7 +4214,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4256,6 +4268,228 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,13 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,18 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2057,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2111,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2490,24 +2498,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2517,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2566,12 +2574,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2599,32 +2607,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2632,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2656,17 +2668,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2676,13 +2688,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2710,32 +2726,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2743,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2767,37 +2787,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2825,32 +2845,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2858,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2882,17 +2906,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2902,13 +2926,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2936,32 +2964,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2969,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2993,17 +3025,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3013,13 +3045,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3047,32 +3083,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3080,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3104,37 +3144,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3234,7 +3274,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3249,7 +3289,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3388,32 +3428,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3421,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3445,33 +3489,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3499,32 +3547,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3532,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3556,37 +3608,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3614,32 +3666,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3647,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3671,37 +3727,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3729,32 +3785,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3762,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3786,17 +3846,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3806,17 +3866,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3916,7 +3976,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3988,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4042,7 +4102,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4163,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,7 +4274,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4325,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4369,13 +4429,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4500,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4480,11 +4544,816 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr"/>
-      <c r="AC35" s="2" t="inlineStr">
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,13 +1883,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,7 +1993,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2104,22 +2108,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,18 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2696,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,22 +2810,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,22 +2929,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3174,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,22 +3282,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,17 +3512,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3584,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3638,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3757,7 +3765,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3795,24 +3803,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3822,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3871,12 +3879,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3904,32 +3912,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3937,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3961,17 +3973,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3981,13 +3993,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4015,32 +4031,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4048,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4072,37 +4092,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4202,7 +4222,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4241,32 +4261,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4274,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4298,33 +4322,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4352,32 +4380,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4385,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4409,17 +4441,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4429,17 +4461,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4467,32 +4499,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4500,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4524,37 +4560,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4582,32 +4618,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4615,7 +4655,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4639,37 +4679,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4697,32 +4737,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4730,7 +4774,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4754,37 +4798,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4899,7 +4943,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4927,32 +4971,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4960,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4984,32 +5032,32 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5075,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5129,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5244,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5252,22 +5300,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5305,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5319,43 +5367,848 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,18 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,12 +2346,12 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2890,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2939,7 +2943,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3063,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3292,12 +3296,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3473,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3527,7 +3531,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,22 +3635,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3988,17 +3992,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4068,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,22 +4111,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,18 +4226,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4337,12 +4345,12 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4471,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4517,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4536,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4585,7 +4593,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4655,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,12 +4755,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -4774,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4823,12 +4831,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4951,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4993,12 +5001,12 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5008,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5062,7 +5070,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5090,32 +5098,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5123,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5147,37 +5159,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5304,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5332,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5353,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5377,37 +5393,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5435,32 +5451,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5468,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5492,32 +5512,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5550,32 +5570,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5583,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5607,27 +5631,27 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5665,32 +5689,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5698,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5722,33 +5750,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5858,7 +5890,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5924,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6088,12 +6120,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6186,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6208,7 +6240,582 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,22 +3286,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,22 +3516,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4583,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4702,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,22 +4821,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5055,22 +5055,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,24 +5699,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5808,32 +5808,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5841,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5865,37 +5869,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5923,32 +5927,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5956,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5980,37 +5988,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6038,32 +6046,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6071,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6095,37 +6107,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6153,32 +6165,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6186,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6210,37 +6226,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6355,7 +6371,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6662,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,7 +6777,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6810,12 +6826,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,22 +3635,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5408,17 +5408,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6187,12 +6187,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,32 +6284,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6317,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6341,37 +6345,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6399,32 +6403,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6432,7 +6440,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6456,32 +6464,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6514,32 +6522,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6547,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6571,17 +6583,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6591,7 +6603,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6662,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7410,6 +7422,236 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,22 +2346,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,17 +2938,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,17 +4116,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,22 +4345,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,17 +5770,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5889,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6403,36 +6403,32 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6440,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6464,17 +6460,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6484,17 +6480,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6532,24 +6528,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6559,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6598,7 +6594,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6608,7 +6604,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6641,32 +6637,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6698,37 +6698,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6756,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6789,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,17 +6817,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6833,17 +6837,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6875,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6904,7 +6912,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6928,17 +6936,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6948,17 +6956,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7257,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7372,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7487,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7533,7 +7541,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7602,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7638,17 +7646,362 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4702,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq21推进至seq32，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4905,10 +4905,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>张杨北路五莲路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4936,7 +4948,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5016,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5072,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5369,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5488,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5607,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5656,12 +5668,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5765,7 +5777,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5775,12 +5787,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5884,7 +5896,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5894,7 +5906,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5964,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6003,22 +6015,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,12 +6139,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6202,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,17 +6258,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6375,7 +6387,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6555,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,24 +6659,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6674,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6723,12 +6735,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6766,24 +6778,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6793,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6832,7 +6844,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6842,12 +6854,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6885,24 +6897,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6912,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6951,7 +6963,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6961,7 +6973,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6994,32 +7006,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7027,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7051,37 +7067,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7109,32 +7125,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7142,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7166,17 +7186,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7186,12 +7206,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7257,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7339,32 +7359,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7372,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7396,17 +7420,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7416,17 +7440,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7541,7 +7565,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,22 +7803,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7827,12 +7851,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7871,22 +7895,18 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7914,7 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -7904,7 +7924,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7942,12 +7962,12 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7961,45 +7981,961 @@
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="V64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr">
+      <c r="W65" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X64" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y64" s="2" t="inlineStr">
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z64" s="2" t="inlineStr">
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
         <is>
           <t>6/18</t>
         </is>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,22 +3635,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5186,22 +5186,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq23推进至seq34，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5270,10 +5270,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5301,7 +5313,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5316,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,17 +5432,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5500,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,17 +5551,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5619,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,7 +5670,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5673,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5857,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5911,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6095,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6134,7 +6146,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6214,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6253,7 +6265,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6263,12 +6275,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6372,22 +6384,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,17 +6499,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6567,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,17 +6618,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6686,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,7 +6737,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6740,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6978,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7162,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7201,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7244,32 +7256,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7277,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,32 +7317,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7369,24 +7385,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7396,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7451,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7445,12 +7461,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7478,32 +7494,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7511,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7535,37 +7555,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7593,32 +7613,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7626,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7650,32 +7674,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7708,32 +7732,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7741,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7765,32 +7793,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7856,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7895,7 +7923,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7934,32 +7962,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7967,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7991,37 +8023,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8197,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8236,7 +8268,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8251,7 +8283,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8423,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8538,7 +8570,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8592,7 +8624,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8685,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8707,7 +8739,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8822,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8915,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8941,6 +8973,1152 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2933,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,22 +3516,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,17 +3873,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,22 +4464,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4583,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,17 +4702,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5067,22 +5067,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,22 +5313,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5789,22 +5789,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,22 +5908,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6027,17 +6027,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,22 +6265,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,22 +6975,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,17 +7094,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8081,32 +8081,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8114,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,32 +8142,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8196,32 +8200,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8229,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8253,17 +8261,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8273,17 +8281,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8383,7 +8391,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8422,32 +8430,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8455,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8479,37 +8491,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8537,32 +8549,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8570,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8594,27 +8610,27 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8624,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8652,32 +8668,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8685,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8709,37 +8729,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8767,32 +8787,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8800,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8824,37 +8848,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8882,32 +8906,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8915,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8939,32 +8967,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -8997,32 +9025,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9030,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9054,37 +9086,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9112,32 +9144,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9145,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9169,17 +9205,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9189,12 +9225,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9227,32 +9263,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9260,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9284,37 +9324,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9415,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9490,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9544,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9645,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9720,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9835,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9889,7 +9929,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9990,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9994,17 +10034,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10105,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10119,6 +10159,1037 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,22 +1878,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,22 +4111,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5432,22 +5432,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5551,22 +5551,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,17 +5675,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,22 +6499,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,17 +7332,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7689,22 +7689,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7808,22 +7808,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9154,24 +9154,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9273,24 +9273,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9382,32 +9382,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9415,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9439,32 +9443,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9497,32 +9501,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9530,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9554,17 +9562,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9574,17 +9582,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9620,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9645,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9669,37 +9681,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9727,32 +9739,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9760,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9784,37 +9800,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9914,7 +9930,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9929,7 +9945,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9957,32 +9973,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9990,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10014,17 +10034,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10034,17 +10054,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10144,7 +10164,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10216,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10270,7 +10290,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10370,7 +10390,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10442,7 +10462,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10496,7 +10516,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10577,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10672,7 +10692,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10726,7 +10746,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10841,7 +10861,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10922,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10956,7 +10976,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11037,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11071,7 +11091,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11152,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11181,12 +11201,809 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,13 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,22 +2699,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,17 +2942,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,22 +3175,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3362,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3477,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3521,17 +3525,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,22 +3758,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,22 +3877,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4072,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,17 +4235,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4355,12 +4359,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,22 +4468,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4592,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4782,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4897,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,22 +4952,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,17 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5680,12 +5684,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,17 +5798,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5913,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6270,17 +6274,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6698,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6747,12 +6751,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,17 +6984,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,7 +7336,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7347,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8118,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8157,22 +8161,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8286,12 +8290,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8396,13 +8400,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,17 +8519,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8625,22 +8633,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8744,22 +8752,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,17 +8876,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9101,22 +9109,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9344,17 +9352,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9458,7 +9466,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9473,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9776,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9983,24 +9991,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10010,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10059,12 +10067,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,32 +10211,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10236,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10260,37 +10272,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10318,32 +10330,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10351,7 +10367,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10375,17 +10391,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10395,13 +10411,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10429,32 +10449,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10462,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10486,17 +10510,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10506,17 +10530,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10544,32 +10568,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10577,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10601,37 +10629,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10659,32 +10687,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10692,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10716,37 +10748,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10774,32 +10806,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10807,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10831,17 +10867,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10851,17 +10887,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,32 +11040,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11037,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11061,37 +11101,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11159,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11152,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11176,17 +11220,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11196,17 +11240,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11311,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11382,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11497,7 +11541,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11536,7 +11580,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11551,7 +11595,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11656,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11727,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11842,7 +11886,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11886,13 +11930,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11953,7 +12001,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12007,6 +12055,581 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,18 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2470,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,18 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3892,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4130,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4483,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4838,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5332,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6994,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,17 +7230,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7825,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,18 +7935,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8161,7 +8173,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8176,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,17 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8752,7 +8764,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8767,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9124,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,17 +9245,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9483,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9612,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9719,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9840,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9955,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10172,18 +10184,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10287,7 +10303,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10302,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10411,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10644,7 +10660,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10659,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10784,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10897,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11278,32 +11294,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11311,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11335,17 +11355,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11355,17 +11375,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11480,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11508,32 +11528,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11541,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11565,17 +11589,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11585,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -11623,32 +11647,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11656,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11680,17 +11708,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11700,17 +11728,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11738,32 +11766,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11771,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11795,17 +11827,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11815,17 +11847,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11853,32 +11885,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11886,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11910,17 +11946,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11930,17 +11966,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11968,32 +12004,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12001,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12025,33 +12065,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB98" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12079,32 +12123,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12112,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12136,17 +12184,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12156,17 +12204,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12266,7 +12314,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12281,7 +12329,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12396,7 +12444,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12496,7 +12544,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12511,7 +12559,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12616,17 +12664,362 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>94.6</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB103" s="2" t="inlineStr">
-        <is>
-          <t>95.5</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-浦东78路.xlsx
+++ b/data/export/2026-10-20-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2708,17 +2708,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,17 +9126,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9483,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,17 +10665,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11137,17 +11137,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -12357,32 +12357,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12390,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12414,17 +12418,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12434,17 +12438,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12472,32 +12476,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12505,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12529,17 +12537,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12549,17 +12557,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12587,32 +12595,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12620,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12644,17 +12656,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12664,17 +12676,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12702,32 +12714,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12735,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12759,17 +12775,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12779,12 +12795,12 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12850,7 +12866,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12904,7 +12920,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12981,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13009,17 +13025,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
